--- a/Лист Microsoft Excel.xlsx
+++ b/Лист Microsoft Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavel\Desktop\diploma2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE13DAF1-7CA0-468A-9DC8-7B5D635FA0AD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC03348-01FF-41F2-ADDF-177792CDAEE4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="55">
   <si>
     <t>Наименование задачи</t>
   </si>
@@ -108,9 +108,6 @@
     <t>Критерий / функция</t>
   </si>
   <si>
-    <t>IT-Cube «Образование» (проект)</t>
-  </si>
-  <si>
     <t>АИС «Навигатор»</t>
   </si>
   <si>
@@ -120,9 +117,6 @@
     <t>Moodle</t>
   </si>
   <si>
-    <t>Каталог программ (ДООП)</t>
-  </si>
-  <si>
     <t>+</t>
   </si>
   <si>
@@ -147,20 +141,62 @@
     <t>Дедлайны</t>
   </si>
   <si>
-    <t>Сдачи работ</t>
-  </si>
-  <si>
     <t>Проверка работ</t>
   </si>
   <si>
     <t>Задания</t>
+  </si>
+  <si>
+    <t>Этап</t>
+  </si>
+  <si>
+    <t>AS-IS, мин.</t>
+  </si>
+  <si>
+    <t>TO-BE, мин.</t>
+  </si>
+  <si>
+    <t>Изменение</t>
+  </si>
+  <si>
+    <t>Формирование курса / управление программами и группами</t>
+  </si>
+  <si>
+    <t>Приём анкет / обработка заявки и запись на собеседование</t>
+  </si>
+  <si>
+    <t>Собеседование и формирование группы / отбор и зачисление</t>
+  </si>
+  <si>
+    <t>Сопровождение обучения</t>
+  </si>
+  <si>
+    <t>Фиксация результатов и отчётность</t>
+  </si>
+  <si>
+    <t>Итого</t>
+  </si>
+  <si>
+    <t>Каталог программ ДПО</t>
+  </si>
+  <si>
+    <t>Сдача работ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Платформа «Поляная Мартица», модуль «Образование» </t>
+  </si>
+  <si>
+    <t>Документ о прохождении</t>
+  </si>
+  <si>
+    <t>Наличие ИИ-ассистента</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,21 +226,6 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -214,7 +235,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -237,63 +258,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -308,16 +277,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -600,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
@@ -608,10 +571,16 @@
     <col min="3" max="3" width="15" style="1" customWidth="1"/>
     <col min="4" max="5" width="8.88671875" style="1"/>
     <col min="6" max="6" width="26" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="11" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="1" customWidth="1"/>
+    <col min="9" max="12" width="8.88671875" style="1"/>
+    <col min="13" max="13" width="6.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -621,23 +590,20 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="61.2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -647,23 +613,20 @@
       <c r="C2" s="5">
         <v>880</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="5">
+        <v>150</v>
+      </c>
+      <c r="N2" s="5">
+        <v>39</v>
+      </c>
+      <c r="O2" s="5">
+        <v>-111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="61.2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -673,23 +636,20 @@
       <c r="C3" s="5">
         <v>112</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" s="5">
+        <v>40</v>
+      </c>
+      <c r="N3" s="5">
+        <v>11</v>
+      </c>
+      <c r="O3" s="5">
+        <v>-29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="61.2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -699,23 +659,20 @@
       <c r="C4" s="5">
         <v>80</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="5">
+        <v>45</v>
+      </c>
+      <c r="N4" s="5">
+        <v>30</v>
+      </c>
+      <c r="O4" s="5">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="30.6" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -725,23 +682,20 @@
       <c r="C5" s="5">
         <v>32</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="5">
+        <v>140</v>
+      </c>
+      <c r="N5" s="5">
+        <v>115</v>
+      </c>
+      <c r="O5" s="5">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="30.6" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -751,23 +705,20 @@
       <c r="C6" s="5">
         <v>144</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" s="5">
+        <v>65</v>
+      </c>
+      <c r="N6" s="5">
+        <v>25</v>
+      </c>
+      <c r="O6" s="5">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -777,23 +728,20 @@
       <c r="C7" s="5">
         <v>40</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="3">
+        <v>440</v>
+      </c>
+      <c r="N7" s="3">
+        <v>220</v>
+      </c>
+      <c r="O7" s="3">
+        <v>-220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -803,23 +751,8 @@
       <c r="C8" s="5">
         <v>56</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -829,23 +762,8 @@
       <c r="C9" s="5">
         <v>24</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -855,23 +773,8 @@
       <c r="C10" s="5">
         <v>24</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -881,23 +784,8 @@
       <c r="C11" s="5">
         <v>160</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -908,7 +796,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30.6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="30.6" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
@@ -919,7 +807,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="51" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
@@ -929,8 +817,23 @@
       <c r="C14" s="5">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
@@ -940,8 +843,23 @@
       <c r="C15" s="5">
         <v>256</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="F15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
@@ -951,8 +869,23 @@
       <c r="C16" s="5">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="F16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
@@ -962,8 +895,23 @@
       <c r="C17" s="5">
         <v>48</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="F17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>19</v>
       </c>
@@ -973,8 +921,23 @@
       <c r="C18" s="5">
         <v>80</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="F18" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
@@ -984,8 +947,23 @@
       <c r="C19" s="5">
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="F19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
@@ -995,8 +973,23 @@
       <c r="C20" s="5">
         <v>144</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="F20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
@@ -1006,8 +999,23 @@
       <c r="C21" s="5">
         <v>80</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>23</v>
       </c>
@@ -1017,8 +1025,23 @@
       <c r="C22" s="5">
         <v>64</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="F22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>24</v>
       </c>
@@ -1028,8 +1051,23 @@
       <c r="C23" s="5">
         <v>40</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="F23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>25</v>
       </c>
@@ -1038,6 +1076,55 @@
       </c>
       <c r="C24" s="5">
         <v>24</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F25" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F26" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Лист Microsoft Excel.xlsx
+++ b/Лист Microsoft Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavel\Desktop\diploma2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC03348-01FF-41F2-ADDF-177792CDAEE4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5059032C-6816-4375-A3D8-AA8514B0ACFB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -563,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
@@ -580,16 +580,7 @@
     <col min="16" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
+    <row r="1" spans="6:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="L1" s="2" t="s">
         <v>40</v>
       </c>
@@ -603,16 +594,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="61.2" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5">
-        <v>110</v>
-      </c>
-      <c r="C2" s="5">
-        <v>880</v>
-      </c>
+    <row r="2" spans="6:15" ht="61.2" x14ac:dyDescent="0.35">
       <c r="L2" s="4" t="s">
         <v>44</v>
       </c>
@@ -626,16 +608,7 @@
         <v>-111</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="61.2" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="5">
-        <v>14</v>
-      </c>
-      <c r="C3" s="5">
-        <v>112</v>
-      </c>
+    <row r="3" spans="6:15" ht="61.2" x14ac:dyDescent="0.35">
       <c r="L3" s="4" t="s">
         <v>45</v>
       </c>
@@ -649,16 +622,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="61.2" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="5">
-        <v>10</v>
-      </c>
-      <c r="C4" s="5">
-        <v>80</v>
-      </c>
+    <row r="4" spans="6:15" ht="61.2" x14ac:dyDescent="0.35">
       <c r="L4" s="4" t="s">
         <v>46</v>
       </c>
@@ -672,16 +636,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="30.6" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5">
-        <v>32</v>
-      </c>
+    <row r="5" spans="6:15" ht="30.6" x14ac:dyDescent="0.35">
       <c r="L5" s="4" t="s">
         <v>47</v>
       </c>
@@ -695,16 +650,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="30.6" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="5">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5">
-        <v>144</v>
-      </c>
+    <row r="6" spans="6:15" ht="30.6" x14ac:dyDescent="0.35">
       <c r="L6" s="4" t="s">
         <v>48</v>
       </c>
@@ -718,16 +664,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5">
-        <v>5</v>
-      </c>
-      <c r="C7" s="5">
-        <v>40</v>
-      </c>
+    <row r="7" spans="6:15" x14ac:dyDescent="0.35">
       <c r="L7" s="6" t="s">
         <v>49</v>
       </c>
@@ -741,82 +678,7 @@
         <v>-220</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="5">
-        <v>7</v>
-      </c>
-      <c r="C8" s="5">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5">
-        <v>3</v>
-      </c>
-      <c r="C9" s="5">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="5">
-        <v>3</v>
-      </c>
-      <c r="C10" s="5">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="5">
-        <v>20</v>
-      </c>
-      <c r="C11" s="5">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="5">
-        <v>5</v>
-      </c>
-      <c r="C12" s="5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="30.6" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="5">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="51" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="5">
-        <v>7</v>
-      </c>
-      <c r="C14" s="5">
-        <v>56</v>
-      </c>
+    <row r="14" spans="6:15" ht="51" x14ac:dyDescent="0.35">
       <c r="F14" s="2" t="s">
         <v>26</v>
       </c>
@@ -833,16 +695,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="5">
-        <v>32</v>
-      </c>
-      <c r="C15" s="5">
-        <v>256</v>
-      </c>
+    <row r="15" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F15" s="7" t="s">
         <v>50</v>
       </c>
@@ -859,16 +712,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="5">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>64</v>
-      </c>
+    <row r="16" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F16" s="7" t="s">
         <v>32</v>
       </c>
@@ -885,16 +729,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="5">
-        <v>6</v>
-      </c>
-      <c r="C17" s="5">
-        <v>48</v>
-      </c>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F17" s="7" t="s">
         <v>36</v>
       </c>
@@ -912,15 +747,6 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="5">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>80</v>
-      </c>
       <c r="F18" s="7" t="s">
         <v>35</v>
       </c>
@@ -937,16 +763,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="5">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>64</v>
-      </c>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F19" s="7" t="s">
         <v>33</v>
       </c>
@@ -964,15 +781,6 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="5">
-        <v>18</v>
-      </c>
-      <c r="C20" s="5">
-        <v>144</v>
-      </c>
       <c r="F20" s="7" t="s">
         <v>34</v>
       </c>
@@ -989,16 +797,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="5">
-        <v>10</v>
-      </c>
-      <c r="C21" s="5">
-        <v>80</v>
-      </c>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F21" s="7" t="s">
         <v>39</v>
       </c>
@@ -1016,15 +815,6 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="5">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>64</v>
-      </c>
       <c r="F22" s="7" t="s">
         <v>37</v>
       </c>
@@ -1041,16 +831,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="5">
-        <v>5</v>
-      </c>
-      <c r="C23" s="5">
-        <v>40</v>
-      </c>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F23" s="7" t="s">
         <v>51</v>
       </c>
@@ -1067,16 +848,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="5">
-        <v>3</v>
-      </c>
-      <c r="C24" s="5">
-        <v>24</v>
-      </c>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F24" s="7" t="s">
         <v>38</v>
       </c>
@@ -1125,6 +897,270 @@
       </c>
       <c r="J26" s="7" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="5">
+        <v>110</v>
+      </c>
+      <c r="C30" s="5">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="5">
+        <v>14</v>
+      </c>
+      <c r="C31" s="5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="5">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="5">
+        <v>4</v>
+      </c>
+      <c r="C33" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="5">
+        <v>18</v>
+      </c>
+      <c r="C34" s="5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="5">
+        <v>5</v>
+      </c>
+      <c r="C35" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="5">
+        <v>7</v>
+      </c>
+      <c r="C36" s="5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="5">
+        <v>3</v>
+      </c>
+      <c r="C37" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="5">
+        <v>3</v>
+      </c>
+      <c r="C38" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="5">
+        <v>20</v>
+      </c>
+      <c r="C39" s="5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="5">
+        <v>5</v>
+      </c>
+      <c r="C40" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="30.6" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="5">
+        <v>8</v>
+      </c>
+      <c r="C41" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="5">
+        <v>7</v>
+      </c>
+      <c r="C42" s="5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="5">
+        <v>32</v>
+      </c>
+      <c r="C43" s="5">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="5">
+        <v>8</v>
+      </c>
+      <c r="C44" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="5">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" s="5">
+        <v>10</v>
+      </c>
+      <c r="C46" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" s="5">
+        <v>8</v>
+      </c>
+      <c r="C47" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="5">
+        <v>18</v>
+      </c>
+      <c r="C48" s="5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="5">
+        <v>10</v>
+      </c>
+      <c r="C49" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="5">
+        <v>8</v>
+      </c>
+      <c r="C50" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="5">
+        <v>5</v>
+      </c>
+      <c r="C51" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" s="5">
+        <v>3</v>
+      </c>
+      <c r="C52" s="5">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Лист Microsoft Excel.xlsx
+++ b/Лист Microsoft Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavel\Desktop\diploma2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5059032C-6816-4375-A3D8-AA8514B0ACFB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87219A5-BFAC-42D6-B36F-1CC29D24AD7E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -602,10 +602,10 @@
         <v>150</v>
       </c>
       <c r="N2" s="5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" s="5">
-        <v>-111</v>
+        <v>-110</v>
       </c>
     </row>
     <row r="3" spans="6:15" ht="61.2" x14ac:dyDescent="0.35">
@@ -616,10 +616,10 @@
         <v>40</v>
       </c>
       <c r="N3" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O3" s="5">
-        <v>-29</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="4" spans="6:15" ht="61.2" x14ac:dyDescent="0.35">
